--- a/week7/homework-survival-multiple-testing.xlsx
+++ b/week7/homework-survival-multiple-testing.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="122">
   <si>
     <t xml:space="preserve">[Description] Kaplan–Meier &amp; Multiple Testing</t>
   </si>
@@ -160,6 +160,9 @@
   </si>
   <si>
     <t xml:space="preserve">read your table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your Answer:</t>
   </si>
   <si>
     <t xml:space="preserve">Why is the drop at t=9 so big?</t>
@@ -1019,7 +1022,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -1243,36 +1246,40 @@
       <c r="A28" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="D28" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="11"/>
       <c r="E28" s="11"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="5" t="str">
-        <f aca="false">IF(F28="","",IF(ROUND(F28,3)=ROUND(7,3),"✓","✗"))</f>
+      <c r="F28" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G28" s="12"/>
+      <c r="H28" s="5" t="str">
+        <f aca="false">IF(G28="","",IF(ROUND(G28,3)=ROUND(7,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" s="11"/>
+      <c r="F30" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C30" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="5" t="str">
-        <f aca="false">IF(F30="","",IF(UPPER(TRIM(F30))=UPPER("small risk set"),"✓","✗"))</f>
+      <c r="G30" s="12"/>
+      <c r="H30" s="5" t="str">
+        <f aca="false">IF(G30="","",IF(UPPER(TRIM(G30))=UPPER("small risk set"),"✓","✗"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D30:E30"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:J30">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -1297,7 +1304,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -1307,35 +1314,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>0.6931</v>
@@ -1343,7 +1350,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B11" s="7" t="n">
         <v>0.05</v>
@@ -1351,7 +1358,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B12" s="7" t="n">
         <v>-0.4055</v>
@@ -1359,15 +1366,15 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>42</v>
@@ -1375,7 +1382,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="5" t="str">
@@ -1385,7 +1392,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="5" t="str">
@@ -1395,7 +1402,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="5" t="str">
@@ -1405,7 +1412,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="5" t="str">
@@ -1415,36 +1422,40 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="11"/>
+        <v>63</v>
+      </c>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="5" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))=UPPER("doubles"),"✓","✗"))</f>
+      <c r="F22" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G22" s="12"/>
+      <c r="H22" s="5" t="str">
+        <f aca="false">IF(G22="","",IF(UPPER(TRIM(G22))=UPPER("doubles"),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D24" s="11"/>
+      <c r="D24" s="11" t="s">
+        <v>65</v>
+      </c>
       <c r="E24" s="11"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="5" t="str">
-        <f aca="false">IF(F24="","",IF(ROUND(F24,3)=ROUND(0.666667,3),"✓","✗"))</f>
+      <c r="F24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G24" s="12"/>
+      <c r="H24" s="5" t="str">
+        <f aca="false">IF(G24="","",IF(ROUND(G24,3)=ROUND(0.666667,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D24:E24"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:J24">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -1469,7 +1480,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -1483,47 +1494,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>42</v>
@@ -1659,57 +1670,63 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="11"/>
+      <c r="D23" s="11" t="s">
+        <v>79</v>
+      </c>
       <c r="E23" s="11"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="5" t="str">
-        <f aca="false">IF(F23="","",IF(ROUND(F23,3)=ROUND(2,3),"✓","✗"))</f>
+      <c r="F23" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G23" s="12"/>
+      <c r="H23" s="5" t="str">
+        <f aca="false">IF(G23="","",IF(ROUND(G23,3)=ROUND(2,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="D25" s="11"/>
+      <c r="D25" s="11" t="s">
+        <v>81</v>
+      </c>
       <c r="E25" s="11"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="5" t="str">
-        <f aca="false">IF(F25="","",IF(ROUND(F25,3)=ROUND(3,3),"✓","✗"))</f>
+      <c r="F25" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G25" s="12"/>
+      <c r="H25" s="5" t="str">
+        <f aca="false">IF(G25="","",IF(ROUND(G25,3)=ROUND(3,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" s="11"/>
+        <v>82</v>
+      </c>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="5" t="str">
-        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))=UPPER("less"),"✓","✗"))</f>
+      <c r="F27" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G27" s="12"/>
+      <c r="H27" s="5" t="str">
+        <f aca="false">IF(G27="","",IF(UPPER(TRIM(G27))=UPPER("less"),"✓","✗"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D27:E27"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:J27">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -1734,7 +1751,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -1746,36 +1763,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>42</v>
@@ -1895,70 +1912,78 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D19" s="11"/>
+      <c r="D19" s="11" t="s">
+        <v>90</v>
+      </c>
       <c r="E19" s="11"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="5" t="str">
-        <f aca="false">IF(F19="","",IF(ROUND(F19,3)=ROUND(6,3),"✓","✗"))</f>
+      <c r="F19" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" s="12"/>
+      <c r="H19" s="5" t="str">
+        <f aca="false">IF(G19="","",IF(ROUND(G19,3)=ROUND(6,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="D21" s="11"/>
+      <c r="D21" s="11" t="s">
+        <v>92</v>
+      </c>
       <c r="E21" s="11"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="5" t="str">
-        <f aca="false">IF(F21="","",IF(ROUND(F21,3)=ROUND(6,3),"✓","✗"))</f>
+      <c r="F21" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G21" s="12"/>
+      <c r="H21" s="5" t="str">
+        <f aca="false">IF(G21="","",IF(ROUND(G21,3)=ROUND(6,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="D23" s="11"/>
+      <c r="D23" s="11" t="s">
+        <v>94</v>
+      </c>
       <c r="E23" s="11"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="5" t="str">
-        <f aca="false">IF(F23="","",IF(ROUND(F23,3)=ROUND(0.6,3),"✓","✗"))</f>
+      <c r="F23" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G23" s="12"/>
+      <c r="H23" s="5" t="str">
+        <f aca="false">IF(G23="","",IF(ROUND(G23,3)=ROUND(0.6,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C25" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D25" s="11"/>
+      <c r="D25" s="11" t="s">
+        <v>96</v>
+      </c>
       <c r="E25" s="11"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="5" t="str">
-        <f aca="false">IF(F25="","",IF(ROUND(F25,3)=ROUND(6,3),"✓","✗"))</f>
+      <c r="F25" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G25" s="12"/>
+      <c r="H25" s="5" t="str">
+        <f aca="false">IF(G25="","",IF(ROUND(G25,3)=ROUND(6,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D25:E25"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:J25">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -1992,38 +2017,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B9" s="7" t="n">
         <v>7</v>
@@ -2031,33 +2056,33 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B18" s="7" t="n">
         <v>0.00625</v>
@@ -2065,36 +2090,36 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B25" s="7" t="n">
         <v>6</v>
@@ -2102,7 +2127,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B26" s="7" t="n">
         <v>6</v>
@@ -2110,10 +2135,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
